--- a/Donnees/Statistiques Démographiques et sociales/Etat Civil/Tableau Etat Civil pour le Portail.xlsx
+++ b/Donnees/Statistiques Démographiques et sociales/Etat Civil/Tableau Etat Civil pour le Portail.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Documents\Ansade_Project\Donnees\Statistiques Démographiques et sociales\Etat Civil\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A23E4D7-FB1A-45A4-A95C-733F0339E233}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D91A781B-F2DA-44CE-92C8-E7FA5F4C77B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="T7.1" sheetId="2" r:id="rId1"/>
@@ -33,9 +33,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="54">
   <si>
-    <t>Tableau 7.1: Nombre des actes de décès enregistrés par wialaya, 2020-2024</t>
-  </si>
-  <si>
     <t>Wilaya</t>
   </si>
   <si>
@@ -90,18 +87,6 @@
     <t>Total Mauritanie</t>
   </si>
   <si>
-    <t>Source : Agence Nationale du Registre des Populations et des Titres Sécurisés, 2024</t>
-  </si>
-  <si>
-    <t>Tableau7.2: Nombre des actes de mariage enregistrés par wialaya, 2020-2024</t>
-  </si>
-  <si>
-    <t>Tableau 7.3: Nombre des citoyens enrôlés par wilaya 2021-2024</t>
-  </si>
-  <si>
-    <t>Tableau 7.4: Nombre des citoyens mauritaniens enrôlés par âge 2020-2024</t>
-  </si>
-  <si>
     <t>Age</t>
   </si>
   <si>
@@ -117,27 +102,18 @@
     <t>Total des enrôlés -Mauritanie</t>
   </si>
   <si>
-    <t>Tableau 7.5: Nombre des citoyens mauritaniens enrôlés par wilaye et par âge, 2024</t>
-  </si>
-  <si>
     <t>Centres à l'étranger</t>
   </si>
   <si>
     <t>Mauritanie</t>
   </si>
   <si>
-    <t>Tableau 7.6: Nombre de décés enregistrés par âge et année de decés 2020-2024</t>
-  </si>
-  <si>
     <t>0-1 an</t>
   </si>
   <si>
     <t>Total</t>
   </si>
   <si>
-    <t>Tableau 7.7:Le nombre de centres connectés par wilaya pour l'année 2024</t>
-  </si>
-  <si>
     <t>Nombre de centres</t>
   </si>
   <si>
@@ -193,6 +169,30 @@
   </si>
   <si>
     <t xml:space="preserve">   Année de decés~2024</t>
+  </si>
+  <si>
+    <t>Source : ANRPTS/2024</t>
+  </si>
+  <si>
+    <t>Tableau 1.4.1: Nombre des actes de décès enregistrés par wilaya, 2020-2024</t>
+  </si>
+  <si>
+    <t>Tableau 1.4.2: Nombre des actes de mariage enregistrés par wilaya, 2020-2024</t>
+  </si>
+  <si>
+    <t>Tableau 1.4.3: Nombre des citoyens enrôlés par wilaya 2021-2024</t>
+  </si>
+  <si>
+    <t>Tableau 1.4.4: Nombre des citoyens mauritaniens enrôlés par âge 2020-2024</t>
+  </si>
+  <si>
+    <t>Tableau 1.4.5: Nombre des citoyens mauritaniens enrôlés par wilaya et par âge, 2024</t>
+  </si>
+  <si>
+    <t>Tableau 1.4.6: Nombre de décès enregistrés par âge et année de décès 2020-2024</t>
+  </si>
+  <si>
+    <t>Tableau 1.4.7: Le nombre de centres connectés par wilaya pour l'année 2024</t>
   </si>
 </sst>
 </file>
@@ -756,7 +756,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.7">
       <c r="A1" s="3" t="s">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -766,27 +766,27 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.7">
       <c r="A2" s="20" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.7">
       <c r="A3" s="6" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B3" s="7">
         <v>5</v>
@@ -806,7 +806,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.7">
       <c r="A4" s="8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B4" s="9">
         <v>276</v>
@@ -826,7 +826,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.7">
       <c r="A5" s="8" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B5" s="9">
         <v>280</v>
@@ -846,7 +846,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.7">
       <c r="A6" s="8" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B6" s="9">
         <v>316</v>
@@ -866,7 +866,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.7">
       <c r="A7" s="8" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B7" s="9">
         <v>263</v>
@@ -886,7 +886,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.7">
       <c r="A8" s="8" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B8" s="9">
         <v>313</v>
@@ -906,7 +906,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.7">
       <c r="A9" s="8" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B9" s="9">
         <v>204</v>
@@ -926,7 +926,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.7">
       <c r="A10" s="8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B10" s="9">
         <v>81</v>
@@ -946,7 +946,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.7">
       <c r="A11" s="8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B11" s="9">
         <v>188</v>
@@ -966,7 +966,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.7">
       <c r="A12" s="8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B12" s="9">
         <v>57</v>
@@ -986,7 +986,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.7">
       <c r="A13" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B13" s="9">
         <v>142</v>
@@ -1006,7 +1006,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.7">
       <c r="A14" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B14" s="9">
         <v>128</v>
@@ -1026,7 +1026,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.7">
       <c r="A15" s="8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B15" s="9">
         <v>16</v>
@@ -1046,7 +1046,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.7">
       <c r="A16" s="8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B16" s="9">
         <v>546</v>
@@ -1066,7 +1066,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.7">
       <c r="A17" s="8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B17" s="9">
         <v>723</v>
@@ -1086,7 +1086,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.7">
       <c r="A18" s="8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B18" s="9">
         <v>768</v>
@@ -1106,7 +1106,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.7">
       <c r="A19" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B19" s="12">
         <f>SUM(B3:B18)</f>
@@ -1131,7 +1131,7 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.7">
       <c r="A20" s="14" t="s">
-        <v>19</v>
+        <v>46</v>
       </c>
       <c r="B20" s="13"/>
       <c r="C20" s="13"/>
@@ -1157,32 +1157,32 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.7">
       <c r="A1" s="3" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.7">
       <c r="A2" s="20" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.7">
       <c r="A3" s="15" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B3" s="16">
         <v>245</v>
@@ -1202,7 +1202,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.7">
       <c r="A4" s="15" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B4" s="10">
         <v>3860</v>
@@ -1222,7 +1222,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.7">
       <c r="A5" s="15" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B5" s="10">
         <v>3625</v>
@@ -1242,7 +1242,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.7">
       <c r="A6" s="15" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B6" s="10">
         <v>4529</v>
@@ -1262,7 +1262,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.7">
       <c r="A7" s="15" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B7" s="10">
         <v>4586</v>
@@ -1282,7 +1282,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.7">
       <c r="A8" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B8" s="10">
         <v>4287</v>
@@ -1302,7 +1302,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.7">
       <c r="A9" s="15" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B9" s="10">
         <v>2303</v>
@@ -1322,7 +1322,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.7">
       <c r="A10" s="15" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B10" s="10">
         <v>1167</v>
@@ -1342,7 +1342,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.7">
       <c r="A11" s="15" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B11" s="10">
         <v>1139</v>
@@ -1362,7 +1362,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.7">
       <c r="A12" s="15" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B12" s="9">
         <v>950</v>
@@ -1382,7 +1382,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.7">
       <c r="A13" s="15" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B13" s="10">
         <v>1973</v>
@@ -1402,7 +1402,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.7">
       <c r="A14" s="15" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B14" s="9">
         <v>935</v>
@@ -1422,7 +1422,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.7">
       <c r="A15" s="15" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B15" s="9">
         <v>349</v>
@@ -1442,7 +1442,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.7">
       <c r="A16" s="15" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B16" s="10">
         <v>3788</v>
@@ -1462,7 +1462,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.7">
       <c r="A17" s="15" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B17" s="10">
         <v>5618</v>
@@ -1482,7 +1482,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.7">
       <c r="A18" s="15" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B18" s="10">
         <v>5473</v>
@@ -1502,7 +1502,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.7">
       <c r="A19" s="18" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B19" s="16">
         <v>44582</v>
@@ -1526,7 +1526,7 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.7">
       <c r="A20" s="14" t="s">
-        <v>19</v>
+        <v>46</v>
       </c>
       <c r="B20" s="13"/>
       <c r="C20" s="13"/>
@@ -1552,7 +1552,7 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.7">
       <c r="A1" s="3" t="s">
-        <v>21</v>
+        <v>49</v>
       </c>
       <c r="H1" s="36"/>
       <c r="I1" s="36"/>
@@ -1560,19 +1560,19 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.7">
       <c r="A2" s="20" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="H2"/>
       <c r="I2"/>
@@ -1580,7 +1580,7 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.7">
       <c r="A3" s="18" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B3" s="16">
         <v>1658</v>
@@ -1600,7 +1600,7 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.7">
       <c r="A4" s="18" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B4" s="16">
         <v>19010</v>
@@ -1620,7 +1620,7 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.7">
       <c r="A5" s="18" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B5" s="16">
         <v>12499</v>
@@ -1640,7 +1640,7 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.7">
       <c r="A6" s="18" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B6" s="16">
         <v>20853</v>
@@ -1660,7 +1660,7 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.7">
       <c r="A7" s="18" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B7" s="16">
         <v>14705</v>
@@ -1680,7 +1680,7 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.7">
       <c r="A8" s="18" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B8" s="16">
         <v>20116</v>
@@ -1700,7 +1700,7 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.7">
       <c r="A9" s="18" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B9" s="16">
         <v>12879</v>
@@ -1720,7 +1720,7 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.7">
       <c r="A10" s="18" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B10" s="16">
         <v>2082</v>
@@ -1740,7 +1740,7 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.7">
       <c r="A11" s="18" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B11" s="16">
         <v>3976</v>
@@ -1760,7 +1760,7 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.7">
       <c r="A12" s="18" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B12" s="16">
         <v>4308</v>
@@ -1780,7 +1780,7 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.7">
       <c r="A13" s="18" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B13" s="16">
         <v>12774</v>
@@ -1800,7 +1800,7 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.7">
       <c r="A14" s="18" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B14" s="16">
         <v>2471</v>
@@ -1820,7 +1820,7 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.7">
       <c r="A15" s="18" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B15" s="16">
         <v>792</v>
@@ -1840,7 +1840,7 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.7">
       <c r="A16" s="18" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B16" s="16">
         <v>15560</v>
@@ -1859,7 +1859,7 @@
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.7">
       <c r="A17" s="18" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B17" s="16">
         <v>23137</v>
@@ -1879,7 +1879,7 @@
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.7">
       <c r="A18" s="18" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B18" s="16">
         <v>18452</v>
@@ -1899,7 +1899,7 @@
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.7">
       <c r="A19" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B19" s="19">
         <f>SUM(B3:B18)</f>
@@ -1923,7 +1923,7 @@
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.7">
       <c r="A20" s="14" t="s">
-        <v>19</v>
+        <v>46</v>
       </c>
       <c r="B20" s="13"/>
       <c r="C20" s="13"/>
@@ -1951,33 +1951,33 @@
   <sheetData>
     <row r="1" spans="1:6" ht="30" x14ac:dyDescent="0.85">
       <c r="A1" s="3" t="s">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="F1" s="1"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.7">
       <c r="A2" s="20" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.7">
       <c r="A3" s="15" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="B3" s="16">
         <v>41885</v>
@@ -1997,7 +1997,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.7">
       <c r="A4" s="15" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="B4" s="16">
         <v>65103</v>
@@ -2017,7 +2017,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.7">
       <c r="A5" s="15" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="B5" s="16">
         <v>19477</v>
@@ -2037,7 +2037,7 @@
     </row>
     <row r="6" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A6" s="20" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B6" s="19">
         <v>128708</v>
@@ -2058,7 +2058,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.7">
       <c r="A7" s="14" t="s">
-        <v>19</v>
+        <v>46</v>
       </c>
       <c r="B7" s="13"/>
       <c r="C7" s="13"/>
@@ -2092,7 +2092,7 @@
   <sheetData>
     <row r="1" spans="1:9" ht="30" x14ac:dyDescent="0.85">
       <c r="A1" s="3" t="s">
-        <v>28</v>
+        <v>51</v>
       </c>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
@@ -2100,36 +2100,36 @@
     </row>
     <row r="2" spans="1:9" s="33" customFormat="1" x14ac:dyDescent="0.7">
       <c r="A2" s="31" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B2" s="32" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="C2" s="32" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="D2" s="32" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="E2" s="32" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="F2" s="32" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="G2" s="32" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="H2" s="32" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="I2" s="32" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.7">
       <c r="A3" s="21" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="B3" s="16">
         <v>930</v>
@@ -2159,7 +2159,7 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.7">
       <c r="A4" s="21" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B4" s="16">
         <v>2804</v>
@@ -2189,7 +2189,7 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.7">
       <c r="A5" s="21" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B5" s="16">
         <v>2648</v>
@@ -2219,7 +2219,7 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.7">
       <c r="A6" s="21" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B6" s="16">
         <v>3858</v>
@@ -2249,7 +2249,7 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.7">
       <c r="A7" s="21" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B7" s="16">
         <v>4609</v>
@@ -2279,7 +2279,7 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.7">
       <c r="A8" s="21" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B8" s="16">
         <v>6366</v>
@@ -2309,7 +2309,7 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.7">
       <c r="A9" s="21" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B9" s="16">
         <v>4428</v>
@@ -2339,7 +2339,7 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.7">
       <c r="A10" s="21" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B10" s="16">
         <v>1549</v>
@@ -2369,7 +2369,7 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.7">
       <c r="A11" s="21" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B11" s="16">
         <v>2903</v>
@@ -2399,7 +2399,7 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.7">
       <c r="A12" s="21" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B12" s="16">
         <v>1664</v>
@@ -2429,7 +2429,7 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.7">
       <c r="A13" s="21" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B13" s="16">
         <v>2738</v>
@@ -2459,7 +2459,7 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.7">
       <c r="A14" s="21" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B14" s="16">
         <v>1416</v>
@@ -2489,7 +2489,7 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.7">
       <c r="A15" s="21" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B15" s="16">
         <v>327</v>
@@ -2519,7 +2519,7 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.7">
       <c r="A16" s="15" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B16" s="16">
         <v>9627</v>
@@ -2548,7 +2548,7 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.7">
       <c r="A17" s="21" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B17" s="16">
         <v>7790</v>
@@ -2577,7 +2577,7 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.7">
       <c r="A18" s="21" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B18" s="16">
         <v>9662</v>
@@ -2607,7 +2607,7 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.7">
       <c r="A19" s="18" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="B19" s="16">
         <f>SUM(B3:B18)</f>
@@ -2644,7 +2644,7 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.7">
       <c r="A20" s="22" t="s">
-        <v>19</v>
+        <v>46</v>
       </c>
       <c r="B20" s="13"/>
       <c r="C20" s="13"/>
@@ -2674,7 +2674,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="28.8" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A1" s="24" t="s">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="B1" s="23"/>
       <c r="C1" s="23"/>
@@ -2684,27 +2684,27 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.7">
       <c r="A2" s="34" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.7">
       <c r="A3" s="25" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="B3" s="10">
         <v>4</v>
@@ -2724,7 +2724,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.7">
       <c r="A4" s="25" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="B4" s="10">
         <v>11</v>
@@ -2744,7 +2744,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.7">
       <c r="A5" s="25" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="B5" s="4">
         <v>4306</v>
@@ -2764,7 +2764,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.7">
       <c r="A6" s="14" t="s">
-        <v>19</v>
+        <v>46</v>
       </c>
       <c r="B6" s="13"/>
       <c r="C6" s="13"/>
@@ -2789,7 +2789,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="26.4" x14ac:dyDescent="0.35">
       <c r="A1" s="23" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="B1" s="26"/>
       <c r="C1" s="27"/>
@@ -2798,15 +2798,15 @@
     </row>
     <row r="2" spans="1:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="35" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B2" s="35" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="24.6" x14ac:dyDescent="0.3">
       <c r="A3" s="28" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B3" s="29">
         <v>7</v>
@@ -2814,7 +2814,7 @@
     </row>
     <row r="4" spans="1:5" ht="24.6" x14ac:dyDescent="0.3">
       <c r="A4" s="28" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B4" s="29">
         <v>14</v>
@@ -2822,7 +2822,7 @@
     </row>
     <row r="5" spans="1:5" ht="24.6" x14ac:dyDescent="0.3">
       <c r="A5" s="28" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B5" s="29">
         <v>9</v>
@@ -2830,7 +2830,7 @@
     </row>
     <row r="6" spans="1:5" ht="24.6" x14ac:dyDescent="0.3">
       <c r="A6" s="28" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B6" s="29">
         <v>11</v>
@@ -2838,7 +2838,7 @@
     </row>
     <row r="7" spans="1:5" ht="24.6" x14ac:dyDescent="0.3">
       <c r="A7" s="28" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B7" s="29">
         <v>10</v>
@@ -2846,7 +2846,7 @@
     </row>
     <row r="8" spans="1:5" ht="24.6" x14ac:dyDescent="0.3">
       <c r="A8" s="28" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B8" s="29">
         <v>16</v>
@@ -2854,7 +2854,7 @@
     </row>
     <row r="9" spans="1:5" ht="24.6" x14ac:dyDescent="0.3">
       <c r="A9" s="28" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B9" s="29">
         <v>15</v>
@@ -2862,7 +2862,7 @@
     </row>
     <row r="10" spans="1:5" ht="24.6" x14ac:dyDescent="0.3">
       <c r="A10" s="28" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B10" s="29">
         <v>4</v>
@@ -2870,7 +2870,7 @@
     </row>
     <row r="11" spans="1:5" ht="24.6" x14ac:dyDescent="0.3">
       <c r="A11" s="28" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B11" s="29">
         <v>3</v>
@@ -2878,7 +2878,7 @@
     </row>
     <row r="12" spans="1:5" ht="24.6" x14ac:dyDescent="0.3">
       <c r="A12" s="28" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B12" s="29">
         <v>6</v>
@@ -2886,7 +2886,7 @@
     </row>
     <row r="13" spans="1:5" ht="24.6" x14ac:dyDescent="0.3">
       <c r="A13" s="28" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B13" s="29">
         <v>6</v>
@@ -2894,7 +2894,7 @@
     </row>
     <row r="14" spans="1:5" ht="24.6" x14ac:dyDescent="0.3">
       <c r="A14" s="28" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B14" s="29">
         <v>3</v>
@@ -2902,7 +2902,7 @@
     </row>
     <row r="15" spans="1:5" ht="24.6" x14ac:dyDescent="0.3">
       <c r="A15" s="28" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B15" s="29">
         <v>1</v>
@@ -2910,7 +2910,7 @@
     </row>
     <row r="16" spans="1:5" ht="24.6" x14ac:dyDescent="0.3">
       <c r="A16" s="28" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B16" s="29">
         <v>3</v>
@@ -2918,7 +2918,7 @@
     </row>
     <row r="17" spans="1:9" ht="24.6" x14ac:dyDescent="0.3">
       <c r="A17" s="28" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B17" s="29">
         <v>4</v>
@@ -2926,7 +2926,7 @@
     </row>
     <row r="18" spans="1:9" ht="24.6" x14ac:dyDescent="0.3">
       <c r="A18" s="28" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B18" s="29">
         <v>5</v>
@@ -2934,7 +2934,7 @@
     </row>
     <row r="19" spans="1:9" ht="24.6" x14ac:dyDescent="0.3">
       <c r="A19" s="28" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B19" s="29">
         <f>SUM(B3:B18)</f>
@@ -2943,7 +2943,7 @@
     </row>
     <row r="20" spans="1:9" ht="21.6" x14ac:dyDescent="0.65">
       <c r="A20" s="14" t="s">
-        <v>19</v>
+        <v>46</v>
       </c>
       <c r="B20" s="13"/>
       <c r="C20" s="13"/>
